--- a/Result/profitability/3406.xlsx
+++ b/Result/profitability/3406.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-2.58</v>
       </c>
       <c r="M2" t="n">
-        <v>7.248749999999999</v>
+        <v>6.4825</v>
       </c>
       <c r="N2" t="n">
-        <v>19.17</v>
+        <v>18.635</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-2.17</v>
       </c>
       <c r="M3" t="n">
-        <v>5.45</v>
+        <v>5.26</v>
       </c>
       <c r="N3" t="n">
-        <v>6.52625</v>
+        <v>7.30375</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.88</v>
       </c>
       <c r="M4" t="n">
-        <v>4.38875</v>
+        <v>4.1825</v>
       </c>
       <c r="N4" t="n">
-        <v>2.415</v>
+        <v>2.69375</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-2.77</v>
       </c>
       <c r="M5" t="n">
-        <v>3.075</v>
+        <v>3.57</v>
       </c>
       <c r="N5" t="n">
-        <v>-3.04625</v>
+        <v>-2.535000000000001</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-1.22</v>
       </c>
       <c r="M6" t="n">
-        <v>2.65625</v>
+        <v>1.85</v>
       </c>
       <c r="N6" t="n">
-        <v>-10.09</v>
+        <v>-10.21</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-2.41</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7875</v>
+        <v>0.245</v>
       </c>
       <c r="N7" t="n">
-        <v>-14.87125</v>
+        <v>-15.0075</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-1.38</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.68875</v>
+        <v>-0.915</v>
       </c>
       <c r="N8" t="n">
-        <v>-17.3925</v>
+        <v>-17.4425</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1775,7 +1775,7 @@
         <v>-1.54875</v>
       </c>
       <c r="N11" t="n">
-        <v>-3.76375</v>
+        <v>-3.763749999999999</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -1902,7 +1902,7 @@
         <v>-1.18375</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2362499999999996</v>
+        <v>0.2362500000000014</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -2029,7 +2029,7 @@
         <v>-0.1074999999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>6.016249999999999</v>
+        <v>6.016250000000001</v>
       </c>
       <c r="O13" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3406</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>5682</v>
+      </c>
+      <c r="D75" t="n">
+        <v>3798</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1884</v>
+      </c>
+      <c r="F75" t="n">
+        <v>33.16</v>
+      </c>
+      <c r="G75" t="n">
+        <v>960</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>16.89%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-142</v>
+      </c>
+      <c r="J75" t="n">
+        <v>818</v>
+      </c>
+      <c r="K75" t="n">
+        <v>686</v>
+      </c>
+      <c r="L75" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="M75" t="n">
+        <v>8.3325</v>
+      </c>
+      <c r="N75" t="n">
+        <v>32.43375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-1.81</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.2291139240506329</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.4000000000000057</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.01191895113230057</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.859154929577465</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>4.089999999999996</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1406948744410044</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
